--- a/rtss-pre1917/output/losses-in-1905-1907.xlsx
+++ b/rtss-pre1917/output/losses-in-1905-1907.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-pre1917\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{799872B6-E457-40C7-A6B9-3B95FE235DC3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C3C2F9-9583-4542-A943-9518A1487B6C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" xr2:uid="{CD6A3FA1-ECCF-46AD-86DE-0432F21AB25D}"/>
+    <workbookView xWindow="2295" yWindow="1635" windowWidth="21165" windowHeight="21885" xr2:uid="{CD6A3FA1-ECCF-46AD-86DE-0432F21AB25D}"/>
   </bookViews>
   <sheets>
     <sheet name="Империя" sheetId="4" r:id="rId1"/>
@@ -112,7 +112,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
-    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -186,11 +186,8 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -209,30 +206,33 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1573,22 +1573,22 @@
   <dimension ref="A1:V39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="19"/>
-    <col min="2" max="2" width="13.5703125" style="19" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" style="20" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="20"/>
-    <col min="5" max="5" width="9.140625" style="19"/>
-    <col min="6" max="7" width="10.140625" style="19" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" style="19" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" style="19" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" style="19" customWidth="1"/>
-    <col min="11" max="12" width="12.7109375" style="19" customWidth="1"/>
-    <col min="13" max="13" width="12.140625" style="19" customWidth="1"/>
-    <col min="14" max="14" width="17.85546875" style="19" customWidth="1"/>
-    <col min="15" max="15" width="13.85546875" style="19" customWidth="1"/>
-    <col min="16" max="20" width="9.140625" style="19"/>
-    <col min="21" max="21" width="20.5703125" style="19" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="19"/>
+    <col min="1" max="1" width="9.140625" style="18"/>
+    <col min="2" max="2" width="13.5703125" style="18" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" style="19" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="19"/>
+    <col min="5" max="5" width="9.140625" style="18"/>
+    <col min="6" max="7" width="10.140625" style="18" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" style="18" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" style="18" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" style="18" customWidth="1"/>
+    <col min="11" max="12" width="12.7109375" style="18" customWidth="1"/>
+    <col min="13" max="13" width="12.140625" style="18" customWidth="1"/>
+    <col min="14" max="14" width="17.85546875" style="18" customWidth="1"/>
+    <col min="15" max="15" width="13.85546875" style="18" customWidth="1"/>
+    <col min="16" max="20" width="9.140625" style="18"/>
+    <col min="21" max="21" width="20.5703125" style="18" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="18"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="18.75" x14ac:dyDescent="0.3">
@@ -1617,10 +1617,10 @@
       <c r="B4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="26" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="6" t="s">
@@ -1669,41 +1669,41 @@
       <c r="A5" s="10">
         <v>1896</v>
       </c>
-      <c r="B5" s="11">
-        <v>124403996</v>
-      </c>
-      <c r="C5" s="21">
-        <v>49.3</v>
-      </c>
-      <c r="D5" s="21">
-        <v>32.1</v>
-      </c>
-      <c r="E5" s="30">
+      <c r="B5" s="29">
+        <v>124402156</v>
+      </c>
+      <c r="C5" s="10">
+        <v>49.4</v>
+      </c>
+      <c r="D5" s="10">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="E5" s="27">
         <v>20573</v>
       </c>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
-      <c r="H5" s="12">
+      <c r="H5" s="11">
         <v>1896</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="12">
         <f>B5*C5/1000</f>
-        <v>6133117.002799999</v>
-      </c>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="12">
+        <v>6145466.5063999994</v>
+      </c>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="11">
         <v>1896</v>
       </c>
-      <c r="M5" s="13">
+      <c r="M5" s="12">
         <f>B5*D5/1000</f>
-        <v>3993368.2716000006</v>
+        <v>4005749.4232000001</v>
       </c>
       <c r="N5" s="8"/>
-      <c r="S5" s="12">
+      <c r="S5" s="11">
         <v>1896</v>
       </c>
-      <c r="T5" s="22">
+      <c r="T5" s="20">
         <f>E5</f>
         <v>20573</v>
       </c>
@@ -1712,41 +1712,41 @@
       <c r="A6" s="10">
         <v>1897</v>
       </c>
-      <c r="B6" s="11">
-        <v>126659599</v>
-      </c>
-      <c r="C6" s="21">
-        <v>49</v>
-      </c>
-      <c r="D6" s="21">
-        <v>30.8</v>
-      </c>
-      <c r="E6" s="30">
+      <c r="B6" s="29">
+        <v>126660365</v>
+      </c>
+      <c r="C6" s="10">
+        <v>49.2</v>
+      </c>
+      <c r="D6" s="10">
+        <v>30.9</v>
+      </c>
+      <c r="E6" s="27">
         <v>63602</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
-      <c r="H6" s="12">
+      <c r="H6" s="11">
         <v>1897</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="12">
         <f t="shared" ref="I6:I22" si="0">B6*C6/1000</f>
-        <v>6206320.3509999998</v>
-      </c>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="12">
+        <v>6231689.9579999996</v>
+      </c>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="11">
         <v>1897</v>
       </c>
-      <c r="M6" s="13">
+      <c r="M6" s="12">
         <f t="shared" ref="M6:M22" si="1">B6*D6/1000</f>
-        <v>3901115.6492000003</v>
+        <v>3913805.2785</v>
       </c>
       <c r="N6" s="8"/>
-      <c r="S6" s="12">
+      <c r="S6" s="11">
         <v>1897</v>
       </c>
-      <c r="T6" s="22">
+      <c r="T6" s="20">
         <f t="shared" ref="T6:T22" si="2">E6</f>
         <v>63602</v>
       </c>
@@ -1755,41 +1755,41 @@
       <c r="A7" s="10">
         <v>1898</v>
       </c>
-      <c r="B7" s="11">
-        <v>128848551</v>
-      </c>
-      <c r="C7" s="21">
-        <v>47.5</v>
-      </c>
-      <c r="D7" s="21">
-        <v>32.1</v>
-      </c>
-      <c r="E7" s="30">
+      <c r="B7" s="29">
+        <v>128850846</v>
+      </c>
+      <c r="C7" s="10">
+        <v>47.7</v>
+      </c>
+      <c r="D7" s="10">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="E7" s="27">
         <v>59624</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="12">
+      <c r="H7" s="11">
         <v>1898</v>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="12">
         <f t="shared" si="0"/>
-        <v>6120306.1725000003</v>
-      </c>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="12">
+        <v>6146185.3542000009</v>
+      </c>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="11">
         <v>1898</v>
       </c>
-      <c r="M7" s="13">
+      <c r="M7" s="12">
         <f t="shared" si="1"/>
-        <v>4136038.4871000005</v>
+        <v>4148997.2412000005</v>
       </c>
       <c r="N7" s="8"/>
-      <c r="S7" s="12">
+      <c r="S7" s="11">
         <v>1898</v>
       </c>
-      <c r="T7" s="22">
+      <c r="T7" s="20">
         <f t="shared" si="2"/>
         <v>59624</v>
       </c>
@@ -1798,41 +1798,41 @@
       <c r="A8" s="10">
         <v>1899</v>
       </c>
-      <c r="B8" s="11">
-        <v>131022662</v>
-      </c>
-      <c r="C8" s="21">
-        <v>48</v>
-      </c>
-      <c r="D8" s="21">
-        <v>30.2</v>
-      </c>
-      <c r="E8" s="30">
+      <c r="B8" s="29">
+        <v>131026209</v>
+      </c>
+      <c r="C8" s="10">
+        <v>48.1</v>
+      </c>
+      <c r="D8" s="10">
+        <v>30.3</v>
+      </c>
+      <c r="E8" s="27">
         <v>40206</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
-      <c r="H8" s="12">
+      <c r="H8" s="11">
         <v>1899</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="12">
         <f t="shared" si="0"/>
-        <v>6289087.7759999996</v>
-      </c>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="12">
+        <v>6302360.652900001</v>
+      </c>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="11">
         <v>1899</v>
       </c>
-      <c r="M8" s="13">
+      <c r="M8" s="12">
         <f t="shared" si="1"/>
-        <v>3956884.3924000002</v>
+        <v>3970094.1327000004</v>
       </c>
       <c r="N8" s="8"/>
-      <c r="S8" s="12">
+      <c r="S8" s="11">
         <v>1899</v>
       </c>
-      <c r="T8" s="22">
+      <c r="T8" s="20">
         <f t="shared" si="2"/>
         <v>40206</v>
       </c>
@@ -1841,41 +1841,41 @@
       <c r="A9" s="10">
         <v>1900</v>
       </c>
-      <c r="B9" s="11">
-        <v>133374183</v>
-      </c>
-      <c r="C9" s="21">
-        <v>48.4</v>
-      </c>
-      <c r="D9" s="21">
-        <v>30.2</v>
-      </c>
-      <c r="E9" s="30">
+      <c r="B9" s="29">
+        <v>133378985</v>
+      </c>
+      <c r="C9" s="10">
+        <v>48.6</v>
+      </c>
+      <c r="D9" s="10">
+        <v>30.3</v>
+      </c>
+      <c r="E9" s="27">
         <v>6798</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
-      <c r="H9" s="12">
+      <c r="H9" s="11">
         <v>1900</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="12">
         <f t="shared" si="0"/>
-        <v>6455310.4572000001</v>
-      </c>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="12">
+        <v>6482218.6710000001</v>
+      </c>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="11">
         <v>1900</v>
       </c>
-      <c r="M9" s="13">
+      <c r="M9" s="12">
         <f t="shared" si="1"/>
-        <v>4027900.3265999998</v>
+        <v>4041383.2455000002</v>
       </c>
       <c r="N9" s="8"/>
-      <c r="S9" s="12">
+      <c r="S9" s="11">
         <v>1900</v>
       </c>
-      <c r="T9" s="22">
+      <c r="T9" s="20">
         <f t="shared" si="2"/>
         <v>6798</v>
       </c>
@@ -1884,41 +1884,41 @@
       <c r="A10" s="10">
         <v>1901</v>
       </c>
-      <c r="B10" s="11">
-        <v>135674531</v>
-      </c>
-      <c r="C10" s="21">
-        <v>47.4</v>
-      </c>
-      <c r="D10" s="21">
-        <v>31</v>
-      </c>
-      <c r="E10" s="30">
+      <c r="B10" s="29">
+        <v>135680595</v>
+      </c>
+      <c r="C10" s="10">
+        <v>47.5</v>
+      </c>
+      <c r="D10" s="10">
+        <v>31.1</v>
+      </c>
+      <c r="E10" s="27">
         <v>20407</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
-      <c r="H10" s="12">
+      <c r="H10" s="11">
         <v>1901</v>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="12">
         <f t="shared" si="0"/>
-        <v>6430972.7693999996</v>
-      </c>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="12">
+        <v>6444828.2625000002</v>
+      </c>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="11">
         <v>1901</v>
       </c>
-      <c r="M10" s="13">
+      <c r="M10" s="12">
         <f t="shared" si="1"/>
-        <v>4205910.4610000001</v>
+        <v>4219666.5044999998</v>
       </c>
       <c r="N10" s="8"/>
-      <c r="S10" s="12">
+      <c r="S10" s="11">
         <v>1901</v>
       </c>
-      <c r="T10" s="22">
+      <c r="T10" s="20">
         <f t="shared" si="2"/>
         <v>20407</v>
       </c>
@@ -1927,41 +1927,41 @@
       <c r="A11" s="10">
         <v>1902</v>
       </c>
-      <c r="B11" s="11">
-        <v>138008678</v>
-      </c>
-      <c r="C11" s="21">
-        <v>48.6</v>
-      </c>
-      <c r="D11" s="21">
-        <v>30.7</v>
-      </c>
-      <c r="E11" s="30">
+      <c r="B11" s="29">
+        <v>138016007</v>
+      </c>
+      <c r="C11" s="10">
+        <v>48.7</v>
+      </c>
+      <c r="D11" s="10">
+        <v>30.8</v>
+      </c>
+      <c r="E11" s="27">
         <v>4557</v>
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
-      <c r="H11" s="12">
+      <c r="H11" s="11">
         <v>1902</v>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="12">
         <f t="shared" si="0"/>
-        <v>6707221.7508000005</v>
-      </c>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="12">
+        <v>6721379.5409000004</v>
+      </c>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="11">
         <v>1902</v>
       </c>
-      <c r="M11" s="13">
+      <c r="M11" s="12">
         <f t="shared" si="1"/>
-        <v>4236866.4145999998</v>
+        <v>4250893.0155999996</v>
       </c>
       <c r="N11" s="8"/>
-      <c r="S11" s="12">
+      <c r="S11" s="11">
         <v>1902</v>
       </c>
-      <c r="T11" s="22">
+      <c r="T11" s="20">
         <f t="shared" si="2"/>
         <v>4557</v>
       </c>
@@ -1970,44 +1970,44 @@
       <c r="A12" s="10">
         <v>1903</v>
       </c>
-      <c r="B12" s="11">
-        <v>140500249</v>
-      </c>
-      <c r="C12" s="21">
-        <v>47.7</v>
-      </c>
-      <c r="D12" s="21">
-        <v>29.1</v>
-      </c>
-      <c r="E12" s="30">
+      <c r="B12" s="29">
+        <v>140508848</v>
+      </c>
+      <c r="C12" s="10">
+        <v>47.8</v>
+      </c>
+      <c r="D12" s="10">
+        <v>29.2</v>
+      </c>
+      <c r="E12" s="27">
         <v>-40101</v>
       </c>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
-      <c r="H12" s="12">
+      <c r="H12" s="11">
         <v>1903</v>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="12">
         <f t="shared" si="0"/>
-        <v>6701861.8772999998</v>
-      </c>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="12">
+        <v>6716322.9343999997</v>
+      </c>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="11">
         <v>1903</v>
       </c>
-      <c r="M12" s="13">
+      <c r="M12" s="12">
         <f t="shared" si="1"/>
-        <v>4088557.2459</v>
+        <v>4102858.3615999999</v>
       </c>
       <c r="N12" s="3">
         <f>AVERAGE(M11:M12)</f>
-        <v>4162711.8302499996</v>
-      </c>
-      <c r="S12" s="12">
+        <v>4176875.6886</v>
+      </c>
+      <c r="S12" s="11">
         <v>1903</v>
       </c>
-      <c r="T12" s="22">
+      <c r="T12" s="20">
         <f t="shared" si="2"/>
         <v>-40101</v>
       </c>
@@ -2016,51 +2016,51 @@
       <c r="A13" s="10">
         <v>1904</v>
       </c>
-      <c r="B13" s="11">
-        <v>143010991</v>
-      </c>
-      <c r="C13" s="21">
-        <v>47.8</v>
-      </c>
-      <c r="D13" s="21">
-        <v>29.5</v>
-      </c>
-      <c r="E13" s="30">
+      <c r="B13" s="29">
+        <v>143020865</v>
+      </c>
+      <c r="C13" s="10">
+        <v>47.9</v>
+      </c>
+      <c r="D13" s="10">
+        <v>29.6</v>
+      </c>
+      <c r="E13" s="27">
         <v>-81471</v>
       </c>
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
-      <c r="H13" s="12">
+      <c r="H13" s="11">
         <v>1904</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="12">
         <f t="shared" si="0"/>
-        <v>6835925.3697999995</v>
+        <v>6850699.4335000003</v>
       </c>
       <c r="J13" s="3">
         <f>AVERAGE(I12:I13)</f>
-        <v>6768893.6235499997</v>
-      </c>
-      <c r="K13" s="13"/>
-      <c r="L13" s="12">
+        <v>6783511.1839499995</v>
+      </c>
+      <c r="K13" s="12"/>
+      <c r="L13" s="11">
         <v>1904</v>
       </c>
-      <c r="M13" s="13">
+      <c r="M13" s="12">
         <f t="shared" si="1"/>
-        <v>4218824.2345000003</v>
-      </c>
-      <c r="N13" s="13">
+        <v>4233417.6040000003</v>
+      </c>
+      <c r="N13" s="12">
         <f>_xlfn.FORECAST.LINEAR(ROW(),CHOOSE({1,2},$N$12,$N$16),CHOOSE({1,2},ROW($N$12),ROW($N$16)))</f>
-        <v>4198584.8240624992</v>
-      </c>
-      <c r="O13" s="22">
+        <v>4209310.1487499997</v>
+      </c>
+      <c r="O13" s="20">
         <f>M13-N13</f>
-        <v>20239.410437501036</v>
-      </c>
-      <c r="S13" s="12">
+        <v>24107.455250000581</v>
+      </c>
+      <c r="S13" s="11">
         <v>1904</v>
       </c>
-      <c r="T13" s="22">
+      <c r="T13" s="20">
         <f t="shared" si="2"/>
         <v>-81471</v>
       </c>
@@ -2073,62 +2073,62 @@
       <c r="A14" s="10">
         <v>1905</v>
       </c>
-      <c r="B14" s="11">
-        <v>145184740</v>
-      </c>
-      <c r="C14" s="21">
-        <v>44.7</v>
-      </c>
-      <c r="D14" s="21">
-        <v>31.1</v>
-      </c>
-      <c r="E14" s="30">
+      <c r="B14" s="29">
+        <v>145195894</v>
+      </c>
+      <c r="C14" s="10">
+        <v>44.8</v>
+      </c>
+      <c r="D14" s="10">
+        <v>31.2</v>
+      </c>
+      <c r="E14" s="27">
         <v>-171743</v>
       </c>
       <c r="F14" s="8"/>
       <c r="G14" s="8"/>
-      <c r="H14" s="14">
+      <c r="H14" s="13">
         <v>1905</v>
       </c>
-      <c r="I14" s="15">
+      <c r="I14" s="14">
         <f t="shared" si="0"/>
-        <v>6489757.8779999996</v>
-      </c>
-      <c r="J14" s="15">
+        <v>6504776.0511999996</v>
+      </c>
+      <c r="J14" s="14">
         <f>_xlfn.FORECAST.LINEAR(ROW(),CHOOSE({1,2},$J$13,$J$16),CHOOSE({1,2},ROW($J$13),ROW($J$16)))</f>
-        <v>6851603.7433833331</v>
-      </c>
-      <c r="K14" s="15">
+        <v>6866607.9786999989</v>
+      </c>
+      <c r="K14" s="14">
         <f>J14-I14</f>
-        <v>361845.86538333353</v>
-      </c>
-      <c r="L14" s="14">
+        <v>361831.92749999929</v>
+      </c>
+      <c r="L14" s="13">
         <v>1905</v>
       </c>
-      <c r="M14" s="15">
+      <c r="M14" s="14">
         <f t="shared" si="1"/>
-        <v>4515245.4139999999</v>
-      </c>
-      <c r="N14" s="15">
+        <v>4530111.8928000005</v>
+      </c>
+      <c r="N14" s="14">
         <f>_xlfn.FORECAST.LINEAR(ROW(),CHOOSE({1,2},$N$12,$N$16),CHOOSE({1,2},ROW($N$12),ROW($N$16)))</f>
-        <v>4234457.8178749997</v>
-      </c>
-      <c r="O14" s="23">
+        <v>4241744.6088999994</v>
+      </c>
+      <c r="O14" s="21">
         <f>M14-N14</f>
-        <v>280787.59612500016</v>
-      </c>
-      <c r="S14" s="14">
+        <v>288367.28390000109</v>
+      </c>
+      <c r="S14" s="13">
         <v>1905</v>
       </c>
-      <c r="T14" s="22">
+      <c r="T14" s="20">
         <f t="shared" si="2"/>
         <v>-171743</v>
       </c>
-      <c r="U14" s="19">
+      <c r="U14" s="18">
         <f>_xlfn.FORECAST.LINEAR(ROW(),CHOOSE({1,2},$U$13,$U$16),CHOOSE({1,2},ROW($U$13),ROW($U$16)))</f>
         <v>-6813.8306878306903</v>
       </c>
-      <c r="V14" s="22">
+      <c r="V14" s="20">
         <f>T14-U14</f>
         <v>-164929.16931216931</v>
       </c>
@@ -2137,62 +2137,62 @@
       <c r="A15" s="10">
         <v>1906</v>
       </c>
-      <c r="B15" s="11">
-        <v>147262241</v>
-      </c>
-      <c r="C15" s="21">
-        <v>46.8</v>
-      </c>
-      <c r="D15" s="21">
-        <v>29.5</v>
-      </c>
-      <c r="E15" s="30">
+      <c r="B15" s="29">
+        <v>147274679</v>
+      </c>
+      <c r="C15" s="10">
+        <v>46.9</v>
+      </c>
+      <c r="D15" s="10">
+        <v>29.6</v>
+      </c>
+      <c r="E15" s="27">
         <v>-204101</v>
       </c>
       <c r="F15" s="8"/>
       <c r="G15" s="8"/>
-      <c r="H15" s="12">
+      <c r="H15" s="11">
         <v>1906</v>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="12">
         <f t="shared" si="0"/>
-        <v>6891872.8787999991</v>
-      </c>
-      <c r="J15" s="13">
+        <v>6907182.4450999992</v>
+      </c>
+      <c r="J15" s="12">
         <f>_xlfn.FORECAST.LINEAR(ROW(),CHOOSE({1,2},$J$13,$J$16),CHOOSE({1,2},ROW($J$13),ROW($J$16)))</f>
-        <v>6934313.8632166665</v>
-      </c>
-      <c r="K15" s="13">
+        <v>6949704.7734499993</v>
+      </c>
+      <c r="K15" s="12">
         <f>J15-I15</f>
-        <v>42440.984416667372</v>
-      </c>
-      <c r="L15" s="12">
+        <v>42522.328350000083</v>
+      </c>
+      <c r="L15" s="11">
         <v>1906</v>
       </c>
-      <c r="M15" s="13">
+      <c r="M15" s="12">
         <f t="shared" si="1"/>
-        <v>4344236.1095000003</v>
-      </c>
-      <c r="N15" s="13">
+        <v>4359330.4984000009</v>
+      </c>
+      <c r="N15" s="12">
         <f>_xlfn.FORECAST.LINEAR(ROW(),CHOOSE({1,2},$N$12,$N$16),CHOOSE({1,2},ROW($N$12),ROW($N$16)))</f>
-        <v>4270330.8116875002</v>
-      </c>
-      <c r="O15" s="22">
+        <v>4274179.0690499991</v>
+      </c>
+      <c r="O15" s="20">
         <f>M15-N15</f>
-        <v>73905.297812500037</v>
-      </c>
-      <c r="S15" s="12">
+        <v>85151.429350001737</v>
+      </c>
+      <c r="S15" s="11">
         <v>1906</v>
       </c>
-      <c r="T15" s="22">
+      <c r="T15" s="20">
         <f t="shared" si="2"/>
         <v>-204101</v>
       </c>
-      <c r="U15" s="19">
+      <c r="U15" s="18">
         <f>_xlfn.FORECAST.LINEAR(ROW(),CHOOSE({1,2},$U$13,$U$16),CHOOSE({1,2},ROW($U$13),ROW($U$16)))</f>
         <v>-24093.772486772476</v>
       </c>
-      <c r="V15" s="22">
+      <c r="V15" s="20">
         <f>T15-U15</f>
         <v>-180007.22751322752</v>
       </c>
@@ -2201,47 +2201,47 @@
       <c r="A16" s="10">
         <v>1907</v>
       </c>
-      <c r="B16" s="11">
-        <v>149774589</v>
-      </c>
-      <c r="C16" s="21">
-        <v>47.3</v>
-      </c>
-      <c r="D16" s="21">
+      <c r="B16" s="29">
+        <v>149788316</v>
+      </c>
+      <c r="C16" s="10">
+        <v>47.4</v>
+      </c>
+      <c r="D16" s="10">
         <v>28.4</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="27">
         <v>-57734</v>
       </c>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
-      <c r="H16" s="12">
+      <c r="H16" s="11">
         <v>1907</v>
       </c>
-      <c r="I16" s="13">
+      <c r="I16" s="12">
         <f t="shared" si="0"/>
-        <v>7084338.0597000001</v>
+        <v>7099966.1783999996</v>
       </c>
       <c r="J16" s="3">
         <f>AVERAGE(I16:I17)</f>
-        <v>7017023.9830499999</v>
-      </c>
-      <c r="K16" s="13"/>
-      <c r="L16" s="12">
+        <v>7032801.5681999996</v>
+      </c>
+      <c r="K16" s="12"/>
+      <c r="L16" s="11">
         <v>1907</v>
       </c>
-      <c r="M16" s="13">
+      <c r="M16" s="12">
         <f t="shared" si="1"/>
-        <v>4253598.3275999995</v>
+        <v>4253988.1743999999</v>
       </c>
       <c r="N16" s="3">
         <f>AVERAGE(M16:M17)</f>
-        <v>4306203.8055000007</v>
-      </c>
-      <c r="S16" s="12">
+        <v>4306613.5291999998</v>
+      </c>
+      <c r="S16" s="11">
         <v>1907</v>
       </c>
-      <c r="T16" s="22">
+      <c r="T16" s="20">
         <f t="shared" si="2"/>
         <v>-57734</v>
       </c>
@@ -2254,41 +2254,41 @@
       <c r="A17" s="10">
         <v>1908</v>
       </c>
-      <c r="B17" s="11">
-        <v>152405919</v>
-      </c>
-      <c r="C17" s="21">
-        <v>45.6</v>
-      </c>
-      <c r="D17" s="21">
+      <c r="B17" s="29">
+        <v>152420940</v>
+      </c>
+      <c r="C17" s="10">
+        <v>45.7</v>
+      </c>
+      <c r="D17" s="10">
         <v>28.6</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="27">
         <v>-3929</v>
       </c>
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
-      <c r="H17" s="12">
+      <c r="H17" s="11">
         <v>1908</v>
       </c>
-      <c r="I17" s="13">
+      <c r="I17" s="12">
         <f t="shared" si="0"/>
-        <v>6949709.9064000007</v>
-      </c>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="12">
+        <v>6965636.9579999996</v>
+      </c>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="11">
         <v>1908</v>
       </c>
-      <c r="M17" s="13">
+      <c r="M17" s="12">
         <f t="shared" si="1"/>
-        <v>4358809.283400001</v>
+        <v>4359238.8839999996</v>
       </c>
       <c r="N17" s="8"/>
-      <c r="S17" s="12">
+      <c r="S17" s="11">
         <v>1908</v>
       </c>
-      <c r="T17" s="22">
+      <c r="T17" s="20">
         <f t="shared" si="2"/>
         <v>-3929</v>
       </c>
@@ -2297,41 +2297,41 @@
       <c r="A18" s="10">
         <v>1909</v>
       </c>
-      <c r="B18" s="11">
-        <v>154866957</v>
-      </c>
-      <c r="C18" s="21">
-        <v>45.8</v>
-      </c>
-      <c r="D18" s="21">
-        <v>30</v>
-      </c>
-      <c r="E18" s="30">
+      <c r="B18" s="29">
+        <v>154883249</v>
+      </c>
+      <c r="C18" s="10">
+        <v>45.9</v>
+      </c>
+      <c r="D18" s="10">
+        <v>30.1</v>
+      </c>
+      <c r="E18" s="27">
         <v>5878</v>
       </c>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
-      <c r="H18" s="12">
+      <c r="H18" s="11">
         <v>1909</v>
       </c>
-      <c r="I18" s="13">
+      <c r="I18" s="12">
         <f t="shared" si="0"/>
-        <v>7092906.6305999998</v>
-      </c>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="12">
+        <v>7109141.1290999996</v>
+      </c>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="11">
         <v>1909</v>
       </c>
-      <c r="M18" s="13">
+      <c r="M18" s="12">
         <f t="shared" si="1"/>
-        <v>4646008.71</v>
+        <v>4661985.794900001</v>
       </c>
       <c r="N18" s="8"/>
-      <c r="S18" s="12">
+      <c r="S18" s="11">
         <v>1909</v>
       </c>
-      <c r="T18" s="22">
+      <c r="T18" s="20">
         <f t="shared" si="2"/>
         <v>5878</v>
       </c>
@@ -2340,41 +2340,41 @@
       <c r="A19" s="10">
         <v>1910</v>
       </c>
-      <c r="B19" s="11">
-        <v>157146260</v>
-      </c>
-      <c r="C19" s="21">
-        <v>46.2</v>
-      </c>
-      <c r="D19" s="21">
+      <c r="B19" s="29">
+        <v>157163827</v>
+      </c>
+      <c r="C19" s="10">
+        <v>46.3</v>
+      </c>
+      <c r="D19" s="10">
         <v>31.5</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="27">
         <v>-86789</v>
       </c>
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
-      <c r="H19" s="12">
+      <c r="H19" s="11">
         <v>1910</v>
       </c>
-      <c r="I19" s="13">
+      <c r="I19" s="12">
         <f t="shared" si="0"/>
-        <v>7260157.2120000003</v>
-      </c>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="12">
+        <v>7276685.1900999993</v>
+      </c>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="11">
         <v>1910</v>
       </c>
-      <c r="M19" s="13">
+      <c r="M19" s="12">
         <f t="shared" si="1"/>
-        <v>4950107.1900000004</v>
+        <v>4950660.5504999999</v>
       </c>
       <c r="N19" s="8"/>
-      <c r="S19" s="12">
+      <c r="S19" s="11">
         <v>1910</v>
       </c>
-      <c r="T19" s="22">
+      <c r="T19" s="20">
         <f t="shared" si="2"/>
         <v>-86789</v>
       </c>
@@ -2383,41 +2383,41 @@
       <c r="A20" s="10">
         <v>1911</v>
       </c>
-      <c r="B20" s="11">
-        <v>159667605</v>
-      </c>
-      <c r="C20" s="21">
-        <v>46</v>
-      </c>
-      <c r="D20" s="21">
-        <v>27.7</v>
-      </c>
-      <c r="E20" s="30">
+      <c r="B20" s="29">
+        <v>159686444</v>
+      </c>
+      <c r="C20" s="10">
+        <v>46.1</v>
+      </c>
+      <c r="D20" s="10">
+        <v>27.8</v>
+      </c>
+      <c r="E20" s="27">
         <v>-16960</v>
       </c>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
-      <c r="H20" s="12">
+      <c r="H20" s="11">
         <v>1911</v>
       </c>
-      <c r="I20" s="13">
+      <c r="I20" s="12">
         <f t="shared" si="0"/>
-        <v>7344709.8300000001</v>
-      </c>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="12">
+        <v>7361545.0684000002</v>
+      </c>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="11">
         <v>1911</v>
       </c>
-      <c r="M20" s="13">
+      <c r="M20" s="12">
         <f t="shared" si="1"/>
-        <v>4422792.6584999999</v>
+        <v>4439283.1431999998</v>
       </c>
       <c r="N20" s="8"/>
-      <c r="S20" s="12">
+      <c r="S20" s="11">
         <v>1911</v>
       </c>
-      <c r="T20" s="22">
+      <c r="T20" s="20">
         <f t="shared" si="2"/>
         <v>-16960</v>
       </c>
@@ -2426,41 +2426,41 @@
       <c r="A21" s="10">
         <v>1912</v>
       </c>
-      <c r="B21" s="11">
-        <v>162507639</v>
-      </c>
-      <c r="C21" s="21">
-        <v>44.9</v>
-      </c>
-      <c r="D21" s="21">
+      <c r="B21" s="29">
+        <v>162527755</v>
+      </c>
+      <c r="C21" s="10">
+        <v>45</v>
+      </c>
+      <c r="D21" s="10">
         <v>26.9</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="27">
         <v>-81648</v>
       </c>
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
-      <c r="H21" s="12">
+      <c r="H21" s="11">
         <v>1912</v>
       </c>
-      <c r="I21" s="13">
+      <c r="I21" s="12">
         <f t="shared" si="0"/>
-        <v>7296592.9910999993</v>
-      </c>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="12">
+        <v>7313748.9749999996</v>
+      </c>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="11">
         <v>1912</v>
       </c>
-      <c r="M21" s="13">
+      <c r="M21" s="12">
         <f t="shared" si="1"/>
-        <v>4371455.4890999999</v>
+        <v>4371996.6095000003</v>
       </c>
       <c r="N21" s="8"/>
-      <c r="S21" s="12">
+      <c r="S21" s="11">
         <v>1912</v>
       </c>
-      <c r="T21" s="22">
+      <c r="T21" s="20">
         <f t="shared" si="2"/>
         <v>-81648</v>
       </c>
@@ -2469,51 +2469,51 @@
       <c r="A22" s="10">
         <v>1913</v>
       </c>
-      <c r="B22" s="11">
-        <v>165239912</v>
-      </c>
-      <c r="C22" s="21">
-        <v>44.4</v>
-      </c>
-      <c r="D22" s="21">
-        <v>27.7</v>
-      </c>
-      <c r="E22" s="30">
+      <c r="B22" s="29">
+        <v>165261347</v>
+      </c>
+      <c r="C22" s="10">
+        <v>44.5</v>
+      </c>
+      <c r="D22" s="10">
+        <v>27.8</v>
+      </c>
+      <c r="E22" s="27">
         <v>-48434</v>
       </c>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="12">
+      <c r="H22" s="11">
         <v>1913</v>
       </c>
-      <c r="I22" s="13">
+      <c r="I22" s="12">
         <f t="shared" si="0"/>
-        <v>7336652.0927999998</v>
-      </c>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="12">
+        <v>7354129.9414999997</v>
+      </c>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
+      <c r="L22" s="11">
         <v>1913</v>
       </c>
-      <c r="M22" s="13">
+      <c r="M22" s="12">
         <f t="shared" si="1"/>
-        <v>4577145.5623999992</v>
+        <v>4594265.4466000004</v>
       </c>
       <c r="N22" s="8"/>
-      <c r="S22" s="12">
+      <c r="S22" s="11">
         <v>1913</v>
       </c>
-      <c r="T22" s="22">
+      <c r="T22" s="20">
         <f t="shared" si="2"/>
         <v>-48434</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A23" s="12"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="12"/>
+      <c r="A23" s="11"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="11"/>
       <c r="F23" s="8"/>
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
@@ -2526,10 +2526,10 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="8"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="17"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="16"/>
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
@@ -2548,23 +2548,23 @@
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
-      <c r="H25" s="26" t="s">
+      <c r="H25" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="I25" s="26"/>
-      <c r="J25" s="26"/>
-      <c r="K25" s="13">
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="12">
         <f>SUM(K14:K15)</f>
-        <v>404286.8498000009</v>
+        <v>404354.25584999938</v>
       </c>
       <c r="L25" s="8"/>
       <c r="M25" s="8"/>
       <c r="N25" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O25" s="22">
+      <c r="O25" s="20">
         <f>SUM(O13:O15)</f>
-        <v>374932.30437500123</v>
+        <v>397626.1685000034</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -2575,20 +2575,20 @@
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="27"/>
-      <c r="J26" s="27"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="24"/>
       <c r="K26" s="8"/>
       <c r="L26" s="8"/>
       <c r="M26" s="8"/>
       <c r="N26" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O26" s="22">
+      <c r="O26" s="20">
         <f>Q26*1</f>
         <v>50952</v>
       </c>
-      <c r="Q26" s="22">
+      <c r="Q26" s="20">
         <v>50952</v>
       </c>
     </row>
@@ -2600,9 +2600,9 @@
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
-      <c r="H27" s="27"/>
-      <c r="I27" s="27"/>
-      <c r="J27" s="27"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="24"/>
+      <c r="J27" s="24"/>
       <c r="K27" s="8"/>
       <c r="L27" s="8"/>
       <c r="M27" s="8"/>
@@ -2616,23 +2616,23 @@
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
       <c r="G28" s="8"/>
-      <c r="H28" s="26" t="s">
+      <c r="H28" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="I28" s="26"/>
-      <c r="J28" s="26"/>
-      <c r="K28" s="13">
+      <c r="I28" s="28"/>
+      <c r="J28" s="28"/>
+      <c r="K28" s="12">
         <f>K25*0.68</f>
-        <v>274915.05786400061</v>
-      </c>
-      <c r="L28" s="13"/>
-      <c r="M28" s="13"/>
+        <v>274960.89397799957</v>
+      </c>
+      <c r="L28" s="12"/>
+      <c r="M28" s="12"/>
       <c r="N28" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="O28" s="22">
+      <c r="O28" s="20">
         <f>O25-O26</f>
-        <v>323980.30437500123</v>
+        <v>346674.1685000034</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -2643,14 +2643,14 @@
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
       <c r="G29" s="8"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
-      <c r="J29" s="27"/>
-      <c r="K29" s="13"/>
-      <c r="L29" s="13"/>
-      <c r="M29" s="13"/>
-      <c r="N29" s="13"/>
-      <c r="O29" s="22"/>
+      <c r="H29" s="24"/>
+      <c r="I29" s="24"/>
+      <c r="J29" s="24"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="12"/>
+      <c r="M29" s="12"/>
+      <c r="N29" s="12"/>
+      <c r="O29" s="20"/>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="8"/>
@@ -2660,14 +2660,14 @@
       <c r="E30" s="8"/>
       <c r="F30" s="8"/>
       <c r="G30" s="8"/>
-      <c r="H30" s="27"/>
-      <c r="I30" s="27"/>
-      <c r="J30" s="27"/>
-      <c r="K30" s="13"/>
-      <c r="L30" s="13"/>
-      <c r="M30" s="13"/>
-      <c r="N30" s="13"/>
-      <c r="O30" s="22"/>
+      <c r="H30" s="24"/>
+      <c r="I30" s="24"/>
+      <c r="J30" s="24"/>
+      <c r="K30" s="12"/>
+      <c r="L30" s="12"/>
+      <c r="M30" s="12"/>
+      <c r="N30" s="12"/>
+      <c r="O30" s="20"/>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" s="8"/>
@@ -2677,19 +2677,19 @@
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
       <c r="G31" s="8"/>
-      <c r="H31" s="26" t="s">
+      <c r="H31" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="I31" s="26"/>
-      <c r="J31" s="26"/>
-      <c r="K31" s="13">
+      <c r="I31" s="28"/>
+      <c r="J31" s="28"/>
+      <c r="K31" s="12">
         <f>K28+O28</f>
-        <v>598895.36223900178</v>
-      </c>
-      <c r="L31" s="13"/>
-      <c r="M31" s="13"/>
-      <c r="N31" s="13"/>
-      <c r="O31" s="22"/>
+        <v>621635.06247800298</v>
+      </c>
+      <c r="L31" s="12"/>
+      <c r="M31" s="12"/>
+      <c r="N31" s="12"/>
+      <c r="O31" s="20"/>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" s="8"/>
@@ -2699,14 +2699,14 @@
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8"/>
-      <c r="H32" s="27"/>
-      <c r="I32" s="27"/>
-      <c r="J32" s="27"/>
-      <c r="K32" s="13"/>
-      <c r="L32" s="13"/>
-      <c r="M32" s="13"/>
-      <c r="N32" s="13"/>
-      <c r="O32" s="22"/>
+      <c r="H32" s="24"/>
+      <c r="I32" s="24"/>
+      <c r="J32" s="24"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="12"/>
+      <c r="N32" s="12"/>
+      <c r="O32" s="20"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="8"/>
@@ -2716,14 +2716,14 @@
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
-      <c r="H33" s="27"/>
-      <c r="I33" s="27"/>
-      <c r="J33" s="27"/>
-      <c r="K33" s="13"/>
-      <c r="L33" s="13"/>
-      <c r="M33" s="13"/>
-      <c r="N33" s="13"/>
-      <c r="O33" s="22"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="24"/>
+      <c r="J33" s="24"/>
+      <c r="K33" s="12"/>
+      <c r="L33" s="12"/>
+      <c r="M33" s="12"/>
+      <c r="N33" s="12"/>
+      <c r="O33" s="20"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="8"/>
@@ -2733,14 +2733,14 @@
       <c r="E34" s="8"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8"/>
-      <c r="H34" s="27"/>
-      <c r="I34" s="27"/>
-      <c r="J34" s="27"/>
-      <c r="K34" s="13"/>
-      <c r="L34" s="13"/>
-      <c r="M34" s="13"/>
-      <c r="N34" s="13"/>
-      <c r="O34" s="22"/>
+      <c r="H34" s="24"/>
+      <c r="I34" s="24"/>
+      <c r="J34" s="24"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="12"/>
+      <c r="M34" s="12"/>
+      <c r="N34" s="12"/>
+      <c r="O34" s="20"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="8"/>
@@ -2750,21 +2750,21 @@
       <c r="E35" s="8"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
-      <c r="H35" s="26" t="s">
+      <c r="H35" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="I35" s="26"/>
-      <c r="J35" s="26"/>
-      <c r="K35" s="18">
+      <c r="I35" s="28"/>
+      <c r="J35" s="28"/>
+      <c r="K35" s="17">
         <f>K31/O26</f>
-        <v>11.754109009244029</v>
-      </c>
-      <c r="L35" s="18"/>
-      <c r="M35" s="18"/>
-      <c r="N35" s="18"/>
-      <c r="O35" s="25">
+        <v>12.200405528301205</v>
+      </c>
+      <c r="L35" s="17"/>
+      <c r="M35" s="17"/>
+      <c r="N35" s="17"/>
+      <c r="O35" s="23">
         <f>O28/O26</f>
-        <v>6.3585394955055978</v>
+        <v>6.8039364205527439</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
@@ -2778,11 +2778,11 @@
       <c r="H36" s="8"/>
       <c r="I36" s="8"/>
       <c r="J36" s="8"/>
-      <c r="K36" s="13"/>
-      <c r="L36" s="13"/>
-      <c r="M36" s="13"/>
-      <c r="N36" s="13"/>
-      <c r="O36" s="22"/>
+      <c r="K36" s="12"/>
+      <c r="L36" s="12"/>
+      <c r="M36" s="12"/>
+      <c r="N36" s="12"/>
+      <c r="O36" s="20"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="8"/>
@@ -2795,11 +2795,11 @@
       <c r="H37" s="8"/>
       <c r="I37" s="8"/>
       <c r="J37" s="8"/>
-      <c r="K37" s="13"/>
-      <c r="L37" s="13"/>
-      <c r="M37" s="13"/>
-      <c r="N37" s="13"/>
-      <c r="O37" s="22"/>
+      <c r="K37" s="12"/>
+      <c r="L37" s="12"/>
+      <c r="M37" s="12"/>
+      <c r="N37" s="12"/>
+      <c r="O37" s="20"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="8"/>
@@ -2923,10 +2923,10 @@
       <c r="B4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="25" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="6" t="s">
@@ -2968,35 +2968,35 @@
       <c r="A5" s="10">
         <v>1896</v>
       </c>
-      <c r="B5" s="11">
-        <v>65415156</v>
-      </c>
-      <c r="C5" s="10">
-        <v>52.6</v>
-      </c>
-      <c r="D5" s="10">
-        <v>36.700000000000003</v>
-      </c>
-      <c r="E5" s="30">
+      <c r="B5" s="29">
+        <v>65413316</v>
+      </c>
+      <c r="C5" s="30">
+        <v>52.9</v>
+      </c>
+      <c r="D5" s="30">
+        <v>36.9</v>
+      </c>
+      <c r="E5" s="27">
         <v>63927</v>
       </c>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
-      <c r="H5" s="12">
+      <c r="H5" s="11">
         <v>1896</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="12">
         <f>B5*C5/1000</f>
-        <v>3440837.2056</v>
-      </c>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="12">
+        <v>3460364.4164</v>
+      </c>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="11">
         <v>1896</v>
       </c>
-      <c r="M5" s="13">
+      <c r="M5" s="12">
         <f>B5*D5/1000</f>
-        <v>2400736.2252000002</v>
+        <v>2413751.3604000001</v>
       </c>
       <c r="N5" s="8"/>
       <c r="O5" s="8"/>
@@ -3010,35 +3010,35 @@
       <c r="A6" s="10">
         <v>1897</v>
       </c>
-      <c r="B6" s="11">
-        <v>66573678</v>
-      </c>
-      <c r="C6" s="10">
-        <v>52.5</v>
-      </c>
-      <c r="D6" s="10">
-        <v>34.6</v>
-      </c>
-      <c r="E6" s="30">
+      <c r="B6" s="29">
+        <v>66574444</v>
+      </c>
+      <c r="C6" s="30">
+        <v>52.8</v>
+      </c>
+      <c r="D6" s="30">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="E6" s="27">
         <v>34340</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
-      <c r="H6" s="12">
+      <c r="H6" s="11">
         <v>1897</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="12">
         <f t="shared" ref="I6:I22" si="0">B6*C6/1000</f>
-        <v>3495118.0950000002</v>
-      </c>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="12">
+        <v>3515130.6431999998</v>
+      </c>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="11">
         <v>1897</v>
       </c>
-      <c r="M6" s="13">
+      <c r="M6" s="12">
         <f t="shared" ref="M6:M22" si="1">B6*D6/1000</f>
-        <v>2303449.2588000004</v>
+        <v>2316790.6511999997</v>
       </c>
       <c r="N6" s="8"/>
       <c r="O6" s="8"/>
@@ -3052,35 +3052,35 @@
       <c r="A7" s="10">
         <v>1898</v>
       </c>
-      <c r="B7" s="11">
-        <v>67663486</v>
-      </c>
-      <c r="C7" s="10">
-        <v>50.4</v>
-      </c>
-      <c r="D7" s="10">
-        <v>36.799999999999997</v>
-      </c>
-      <c r="E7" s="30">
+      <c r="B7" s="29">
+        <v>67665782</v>
+      </c>
+      <c r="C7" s="30">
+        <v>50.6</v>
+      </c>
+      <c r="D7" s="30">
+        <v>37</v>
+      </c>
+      <c r="E7" s="27">
         <v>40485</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="12">
+      <c r="H7" s="11">
         <v>1898</v>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="12">
         <f t="shared" si="0"/>
-        <v>3410239.6943999999</v>
-      </c>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="12">
+        <v>3423888.5692000003</v>
+      </c>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="11">
         <v>1898</v>
       </c>
-      <c r="M7" s="13">
+      <c r="M7" s="12">
         <f t="shared" si="1"/>
-        <v>2490016.2847999996</v>
+        <v>2503633.9339999999</v>
       </c>
       <c r="N7" s="8"/>
       <c r="O7" s="8"/>
@@ -3094,35 +3094,35 @@
       <c r="A8" s="10">
         <v>1899</v>
       </c>
-      <c r="B8" s="11">
-        <v>68755751</v>
-      </c>
-      <c r="C8" s="10">
-        <v>50.9</v>
-      </c>
-      <c r="D8" s="10">
-        <v>33.4</v>
-      </c>
-      <c r="E8" s="30">
+      <c r="B8" s="29">
+        <v>68759297</v>
+      </c>
+      <c r="C8" s="30">
+        <v>51.2</v>
+      </c>
+      <c r="D8" s="30">
+        <v>33.5</v>
+      </c>
+      <c r="E8" s="27">
         <v>30853</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
-      <c r="H8" s="12">
+      <c r="H8" s="11">
         <v>1899</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="12">
         <f t="shared" si="0"/>
-        <v>3499667.7259</v>
-      </c>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="12">
+        <v>3520476.0064000003</v>
+      </c>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="11">
         <v>1899</v>
       </c>
-      <c r="M8" s="13">
+      <c r="M8" s="12">
         <f t="shared" si="1"/>
-        <v>2296442.0833999999</v>
+        <v>2303436.4495000001</v>
       </c>
       <c r="N8" s="8"/>
       <c r="O8" s="8"/>
@@ -3136,35 +3136,35 @@
       <c r="A9" s="10">
         <v>1900</v>
       </c>
-      <c r="B9" s="11">
-        <v>70018356</v>
-      </c>
-      <c r="C9" s="10">
-        <v>51.6</v>
-      </c>
-      <c r="D9" s="10">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="E9" s="30">
+      <c r="B9" s="29">
+        <v>70023158</v>
+      </c>
+      <c r="C9" s="30">
+        <v>51.9</v>
+      </c>
+      <c r="D9" s="30">
+        <v>34.4</v>
+      </c>
+      <c r="E9" s="27">
         <v>82832</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
-      <c r="H9" s="12">
+      <c r="H9" s="11">
         <v>1900</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="12">
         <f t="shared" si="0"/>
-        <v>3612947.1695999997</v>
-      </c>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="12">
+        <v>3634201.9002</v>
+      </c>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="11">
         <v>1900</v>
       </c>
-      <c r="M9" s="13">
+      <c r="M9" s="12">
         <f t="shared" si="1"/>
-        <v>2394627.7752000005</v>
+        <v>2408796.6351999999</v>
       </c>
       <c r="N9" s="8"/>
       <c r="O9" s="8"/>
@@ -3178,35 +3178,35 @@
       <c r="A10" s="10">
         <v>1901</v>
       </c>
-      <c r="B10" s="11">
-        <v>71269373</v>
-      </c>
-      <c r="C10" s="10">
-        <v>51.3</v>
-      </c>
-      <c r="D10" s="10">
-        <v>35.4</v>
-      </c>
-      <c r="E10" s="30">
+      <c r="B10" s="29">
+        <v>71275437</v>
+      </c>
+      <c r="C10" s="30">
+        <v>51.5</v>
+      </c>
+      <c r="D10" s="30">
+        <v>35.6</v>
+      </c>
+      <c r="E10" s="27">
         <v>72876</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
-      <c r="H10" s="12">
+      <c r="H10" s="11">
         <v>1901</v>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="12">
         <f t="shared" si="0"/>
-        <v>3656118.8348999997</v>
-      </c>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="12">
+        <v>3670685.0055</v>
+      </c>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="11">
         <v>1901</v>
       </c>
-      <c r="M10" s="13">
+      <c r="M10" s="12">
         <f t="shared" si="1"/>
-        <v>2522935.8041999997</v>
+        <v>2537405.5572000002</v>
       </c>
       <c r="N10" s="8"/>
       <c r="O10" s="8"/>
@@ -3220,35 +3220,35 @@
       <c r="A11" s="10">
         <v>1902</v>
       </c>
-      <c r="B11" s="11">
-        <v>72514926</v>
-      </c>
-      <c r="C11" s="10">
-        <v>52.1</v>
-      </c>
-      <c r="D11" s="10">
-        <v>35.200000000000003</v>
-      </c>
-      <c r="E11" s="30">
+      <c r="B11" s="29">
+        <v>72522254</v>
+      </c>
+      <c r="C11" s="30">
+        <v>52.4</v>
+      </c>
+      <c r="D11" s="30">
+        <v>35.4</v>
+      </c>
+      <c r="E11" s="27">
         <v>66287</v>
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
-      <c r="H11" s="12">
+      <c r="H11" s="11">
         <v>1902</v>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="12">
         <f t="shared" si="0"/>
-        <v>3778027.6445999998</v>
-      </c>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="12">
+        <v>3800166.1096000001</v>
+      </c>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="11">
         <v>1902</v>
       </c>
-      <c r="M11" s="13">
+      <c r="M11" s="12">
         <f t="shared" si="1"/>
-        <v>2552525.3952000001</v>
+        <v>2567287.7916000001</v>
       </c>
       <c r="N11" s="8"/>
       <c r="O11" s="8"/>
@@ -3262,39 +3262,39 @@
       <c r="A12" s="10">
         <v>1903</v>
       </c>
-      <c r="B12" s="11">
-        <v>73880816</v>
-      </c>
-      <c r="C12" s="10">
-        <v>51.7</v>
-      </c>
-      <c r="D12" s="10">
-        <v>32.700000000000003</v>
-      </c>
-      <c r="E12" s="30">
+      <c r="B12" s="29">
+        <v>73889414</v>
+      </c>
+      <c r="C12" s="30">
+        <v>52</v>
+      </c>
+      <c r="D12" s="30">
+        <v>32.9</v>
+      </c>
+      <c r="E12" s="27">
         <v>46579</v>
       </c>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
-      <c r="H12" s="12">
+      <c r="H12" s="11">
         <v>1903</v>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="12">
         <f t="shared" si="0"/>
-        <v>3819638.1872000005</v>
-      </c>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="12">
+        <v>3842249.5279999999</v>
+      </c>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="11">
         <v>1903</v>
       </c>
-      <c r="M12" s="13">
+      <c r="M12" s="12">
         <f t="shared" si="1"/>
-        <v>2415902.6832000003</v>
+        <v>2430961.7206000001</v>
       </c>
       <c r="N12" s="3">
         <f>AVERAGE(M11:M12)</f>
-        <v>2484214.0392000005</v>
+        <v>2499124.7560999999</v>
       </c>
       <c r="O12" s="8"/>
       <c r="P12" s="8"/>
@@ -3307,46 +3307,46 @@
       <c r="A13" s="10">
         <v>1904</v>
       </c>
-      <c r="B13" s="11">
-        <v>75314330</v>
-      </c>
-      <c r="C13" s="10">
-        <v>52</v>
-      </c>
-      <c r="D13" s="10">
-        <v>33.1</v>
-      </c>
-      <c r="E13" s="30">
+      <c r="B13" s="29">
+        <v>75324248</v>
+      </c>
+      <c r="C13" s="30">
+        <v>52.2</v>
+      </c>
+      <c r="D13" s="30">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="E13" s="27">
         <v>2837</v>
       </c>
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
-      <c r="H13" s="12">
+      <c r="H13" s="11">
         <v>1904</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="12">
         <f t="shared" si="0"/>
-        <v>3916345.16</v>
+        <v>3931925.7456000005</v>
       </c>
       <c r="J13" s="3">
         <f>AVERAGE(I12:I13)</f>
-        <v>3867991.6736000003</v>
-      </c>
-      <c r="K13" s="13"/>
-      <c r="L13" s="12">
+        <v>3887087.6368000004</v>
+      </c>
+      <c r="K13" s="12"/>
+      <c r="L13" s="11">
         <v>1904</v>
       </c>
-      <c r="M13" s="13">
+      <c r="M13" s="12">
         <f t="shared" si="1"/>
-        <v>2492904.3229999999</v>
-      </c>
-      <c r="N13" s="13">
+        <v>2508297.4583999994</v>
+      </c>
+      <c r="N13" s="12">
         <f>_xlfn.FORECAST.LINEAR(ROW(),CHOOSE({1,2},$N$12,$N$16),CHOOSE({1,2},ROW($N$12),ROW($N$16)))</f>
-        <v>2511399.0915000001</v>
-      </c>
-      <c r="O13" s="13">
+        <v>2525716.0706000002</v>
+      </c>
+      <c r="O13" s="12">
         <f>M13-N13</f>
-        <v>-18494.768500000238</v>
+        <v>-17418.612200000789</v>
       </c>
       <c r="P13" s="8"/>
       <c r="Q13" s="8"/>
@@ -3358,49 +3358,49 @@
       <c r="A14" s="10">
         <v>1905</v>
       </c>
-      <c r="B14" s="11">
-        <v>76556452</v>
-      </c>
-      <c r="C14" s="10">
-        <v>48.4</v>
-      </c>
-      <c r="D14" s="10">
-        <v>34.5</v>
-      </c>
-      <c r="E14" s="30">
+      <c r="B14" s="29">
+        <v>76567737</v>
+      </c>
+      <c r="C14" s="30">
+        <v>48.6</v>
+      </c>
+      <c r="D14" s="30">
+        <v>34.700000000000003</v>
+      </c>
+      <c r="E14" s="27">
         <v>1525</v>
       </c>
       <c r="F14" s="8"/>
       <c r="G14" s="8"/>
-      <c r="H14" s="14">
+      <c r="H14" s="13">
         <v>1905</v>
       </c>
-      <c r="I14" s="15">
+      <c r="I14" s="14">
         <f t="shared" si="0"/>
-        <v>3705332.2767999996</v>
-      </c>
-      <c r="J14" s="15">
+        <v>3721192.0182000003</v>
+      </c>
+      <c r="J14" s="14">
         <f>_xlfn.FORECAST.LINEAR(ROW(),CHOOSE({1,2},$J$13,$J$16),CHOOSE({1,2},ROW($J$13),ROW($J$16)))</f>
-        <v>3916895.5918166665</v>
-      </c>
-      <c r="K14" s="15">
+        <v>3935213.0635333331</v>
+      </c>
+      <c r="K14" s="14">
         <f>J14-I14</f>
-        <v>211563.31501666689</v>
-      </c>
-      <c r="L14" s="14">
+        <v>214021.04533333285</v>
+      </c>
+      <c r="L14" s="13">
         <v>1905</v>
       </c>
-      <c r="M14" s="15">
+      <c r="M14" s="14">
         <f t="shared" si="1"/>
-        <v>2641197.594</v>
-      </c>
-      <c r="N14" s="15">
+        <v>2656900.4739000001</v>
+      </c>
+      <c r="N14" s="14">
         <f>_xlfn.FORECAST.LINEAR(ROW(),CHOOSE({1,2},$N$12,$N$16),CHOOSE({1,2},ROW($N$12),ROW($N$16)))</f>
-        <v>2538584.1438000002</v>
-      </c>
-      <c r="O14" s="15">
+        <v>2552307.3851000001</v>
+      </c>
+      <c r="O14" s="14">
         <f>M14-N14</f>
-        <v>102613.45019999985</v>
+        <v>104593.08880000003</v>
       </c>
       <c r="P14" s="8"/>
       <c r="Q14" s="8"/>
@@ -3412,49 +3412,49 @@
       <c r="A15" s="10">
         <v>1906</v>
       </c>
-      <c r="B15" s="11">
-        <v>77779872</v>
-      </c>
-      <c r="C15" s="10">
-        <v>50.9</v>
-      </c>
-      <c r="D15" s="10">
-        <v>33.4</v>
-      </c>
-      <c r="E15" s="30">
+      <c r="B15" s="29">
+        <v>77792482</v>
+      </c>
+      <c r="C15" s="30">
+        <v>51.1</v>
+      </c>
+      <c r="D15" s="30">
+        <v>33.5</v>
+      </c>
+      <c r="E15" s="27">
         <v>28979</v>
       </c>
       <c r="F15" s="8"/>
       <c r="G15" s="8"/>
-      <c r="H15" s="12">
+      <c r="H15" s="11">
         <v>1906</v>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="12">
         <f t="shared" si="0"/>
-        <v>3958995.4847999997</v>
-      </c>
-      <c r="J15" s="13">
+        <v>3975195.8302000002</v>
+      </c>
+      <c r="J15" s="12">
         <f>_xlfn.FORECAST.LINEAR(ROW(),CHOOSE({1,2},$J$13,$J$16),CHOOSE({1,2},ROW($J$13),ROW($J$16)))</f>
-        <v>3965799.5100333332</v>
-      </c>
-      <c r="K15" s="13">
+        <v>3983338.4902666663</v>
+      </c>
+      <c r="K15" s="12">
         <f>J15-I15</f>
-        <v>6804.0252333334647</v>
-      </c>
-      <c r="L15" s="12">
+        <v>8142.6600666660815</v>
+      </c>
+      <c r="L15" s="11">
         <v>1906</v>
       </c>
-      <c r="M15" s="13">
+      <c r="M15" s="12">
         <f t="shared" si="1"/>
-        <v>2597847.7247999995</v>
-      </c>
-      <c r="N15" s="13">
+        <v>2606048.1469999999</v>
+      </c>
+      <c r="N15" s="12">
         <f>_xlfn.FORECAST.LINEAR(ROW(),CHOOSE({1,2},$N$12,$N$16),CHOOSE({1,2},ROW($N$12),ROW($N$16)))</f>
-        <v>2565769.1961000003</v>
-      </c>
-      <c r="O15" s="13">
+        <v>2578898.6995999999</v>
+      </c>
+      <c r="O15" s="12">
         <f>M15-N15</f>
-        <v>32078.528699999209</v>
+        <v>27149.447399999946</v>
       </c>
       <c r="P15" s="8"/>
       <c r="Q15" s="8"/>
@@ -3466,42 +3466,42 @@
       <c r="A16" s="10">
         <v>1907</v>
       </c>
-      <c r="B16" s="11">
-        <v>79330486</v>
-      </c>
-      <c r="C16" s="10">
-        <v>50.9</v>
-      </c>
-      <c r="D16" s="10">
-        <v>32.1</v>
-      </c>
-      <c r="E16" s="30">
+      <c r="B16" s="29">
+        <v>79344385</v>
+      </c>
+      <c r="C16" s="30">
+        <v>51.1</v>
+      </c>
+      <c r="D16" s="30">
+        <v>32.200000000000003</v>
+      </c>
+      <c r="E16" s="27">
         <v>231385</v>
       </c>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
-      <c r="H16" s="12">
+      <c r="H16" s="11">
         <v>1907</v>
       </c>
-      <c r="I16" s="13">
+      <c r="I16" s="12">
         <f t="shared" si="0"/>
-        <v>4037921.7374</v>
+        <v>4054498.0734999999</v>
       </c>
       <c r="J16" s="3">
         <f>AVERAGE(I16:I17)</f>
-        <v>4014703.4282499999</v>
-      </c>
-      <c r="K16" s="13"/>
-      <c r="L16" s="12">
+        <v>4031463.9169999999</v>
+      </c>
+      <c r="K16" s="12"/>
+      <c r="L16" s="11">
         <v>1907</v>
       </c>
-      <c r="M16" s="13">
+      <c r="M16" s="12">
         <f t="shared" si="1"/>
-        <v>2546508.6006</v>
+        <v>2554889.1970000002</v>
       </c>
       <c r="N16" s="3">
         <f>AVERAGE(M16:M17)</f>
-        <v>2592954.2483999999</v>
+        <v>2605490.0141000003</v>
       </c>
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
@@ -3514,35 +3514,35 @@
       <c r="A17" s="10">
         <v>1908</v>
       </c>
-      <c r="B17" s="11">
-        <v>80963187</v>
-      </c>
-      <c r="C17" s="10">
-        <v>49.3</v>
-      </c>
-      <c r="D17" s="10">
-        <v>32.6</v>
-      </c>
-      <c r="E17" s="30">
+      <c r="B17" s="29">
+        <v>80978379</v>
+      </c>
+      <c r="C17" s="30">
+        <v>49.5</v>
+      </c>
+      <c r="D17" s="30">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="E17" s="27">
         <v>198764</v>
       </c>
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
-      <c r="H17" s="12">
+      <c r="H17" s="11">
         <v>1908</v>
       </c>
-      <c r="I17" s="13">
+      <c r="I17" s="12">
         <f t="shared" si="0"/>
-        <v>3991485.1190999998</v>
-      </c>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="12">
+        <v>4008429.7604999999</v>
+      </c>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="11">
         <v>1908</v>
       </c>
-      <c r="M17" s="13">
+      <c r="M17" s="12">
         <f t="shared" si="1"/>
-        <v>2639399.8962000003</v>
+        <v>2656090.8311999999</v>
       </c>
       <c r="N17" s="8"/>
       <c r="O17" s="8"/>
@@ -3556,35 +3556,35 @@
       <c r="A18" s="10">
         <v>1909</v>
       </c>
-      <c r="B18" s="11">
-        <v>82453989</v>
-      </c>
-      <c r="C18" s="10">
-        <v>49.7</v>
-      </c>
-      <c r="D18" s="10">
-        <v>34.4</v>
-      </c>
-      <c r="E18" s="30">
+      <c r="B18" s="29">
+        <v>82470452</v>
+      </c>
+      <c r="C18" s="30">
+        <v>49.9</v>
+      </c>
+      <c r="D18" s="30">
+        <v>34.5</v>
+      </c>
+      <c r="E18" s="27">
         <v>171814</v>
       </c>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
-      <c r="H18" s="12">
+      <c r="H18" s="11">
         <v>1909</v>
       </c>
-      <c r="I18" s="13">
+      <c r="I18" s="12">
         <f t="shared" si="0"/>
-        <v>4097963.2533</v>
-      </c>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="12">
+        <v>4115275.5547999996</v>
+      </c>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="11">
         <v>1909</v>
       </c>
-      <c r="M18" s="13">
+      <c r="M18" s="12">
         <f t="shared" si="1"/>
-        <v>2836417.2215999998</v>
+        <v>2845230.594</v>
       </c>
       <c r="N18" s="8"/>
       <c r="O18" s="8"/>
@@ -3598,35 +3598,35 @@
       <c r="A19" s="10">
         <v>1910</v>
       </c>
-      <c r="B19" s="11">
-        <v>83857153</v>
-      </c>
-      <c r="C19" s="10">
-        <v>50.6</v>
-      </c>
-      <c r="D19" s="10">
-        <v>35.5</v>
-      </c>
-      <c r="E19" s="30">
+      <c r="B19" s="29">
+        <v>83874891</v>
+      </c>
+      <c r="C19" s="30">
+        <v>50.8</v>
+      </c>
+      <c r="D19" s="30">
+        <v>35.6</v>
+      </c>
+      <c r="E19" s="27">
         <v>110396</v>
       </c>
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
-      <c r="H19" s="12">
+      <c r="H19" s="11">
         <v>1910</v>
       </c>
-      <c r="I19" s="13">
+      <c r="I19" s="12">
         <f t="shared" si="0"/>
-        <v>4243171.9418000001</v>
-      </c>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="12">
+        <v>4260844.4627999999</v>
+      </c>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="11">
         <v>1910</v>
       </c>
-      <c r="M19" s="13">
+      <c r="M19" s="12">
         <f t="shared" si="1"/>
-        <v>2976928.9314999999</v>
+        <v>2985946.1195999999</v>
       </c>
       <c r="N19" s="8"/>
       <c r="O19" s="8"/>
@@ -3640,35 +3640,35 @@
       <c r="A20" s="10">
         <v>1911</v>
       </c>
-      <c r="B20" s="11">
-        <v>85364340</v>
-      </c>
-      <c r="C20" s="10">
-        <v>50.2</v>
-      </c>
-      <c r="D20" s="10">
-        <v>31.4</v>
-      </c>
-      <c r="E20" s="30">
+      <c r="B20" s="29">
+        <v>85383352</v>
+      </c>
+      <c r="C20" s="30">
+        <v>50.4</v>
+      </c>
+      <c r="D20" s="30">
+        <v>31.5</v>
+      </c>
+      <c r="E20" s="27">
         <v>43236</v>
       </c>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
-      <c r="H20" s="12">
+      <c r="H20" s="11">
         <v>1911</v>
       </c>
-      <c r="I20" s="13">
+      <c r="I20" s="12">
         <f t="shared" si="0"/>
-        <v>4285289.8680000007</v>
-      </c>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="12">
+        <v>4303320.9408</v>
+      </c>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="11">
         <v>1911</v>
       </c>
-      <c r="M20" s="13">
+      <c r="M20" s="12">
         <f t="shared" si="1"/>
-        <v>2680440.2760000001</v>
+        <v>2689575.588</v>
       </c>
       <c r="N20" s="8"/>
       <c r="O20" s="8"/>
@@ -3682,35 +3682,35 @@
       <c r="A21" s="10">
         <v>1912</v>
       </c>
-      <c r="B21" s="11">
-        <v>86955593</v>
-      </c>
-      <c r="C21" s="10">
-        <v>48.3</v>
-      </c>
-      <c r="D21" s="10">
-        <v>31</v>
-      </c>
-      <c r="E21" s="30">
+      <c r="B21" s="29">
+        <v>86975881</v>
+      </c>
+      <c r="C21" s="30">
+        <v>48.5</v>
+      </c>
+      <c r="D21" s="30">
+        <v>31.1</v>
+      </c>
+      <c r="E21" s="27">
         <v>37232</v>
       </c>
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
-      <c r="H21" s="12">
+      <c r="H21" s="11">
         <v>1912</v>
       </c>
-      <c r="I21" s="13">
+      <c r="I21" s="12">
         <f t="shared" si="0"/>
-        <v>4199955.1418999992</v>
-      </c>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="12">
+        <v>4218330.2285000002</v>
+      </c>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="11">
         <v>1912</v>
       </c>
-      <c r="M21" s="13">
+      <c r="M21" s="12">
         <f t="shared" si="1"/>
-        <v>2695623.3829999999</v>
+        <v>2704949.8991</v>
       </c>
       <c r="N21" s="8"/>
       <c r="O21" s="8"/>
@@ -3724,35 +3724,35 @@
       <c r="A22" s="10">
         <v>1913</v>
       </c>
-      <c r="B22" s="11">
-        <v>88498557</v>
-      </c>
-      <c r="C22" s="10">
-        <v>48.2</v>
-      </c>
-      <c r="D22" s="10">
-        <v>31.5</v>
-      </c>
-      <c r="E22" s="30">
+      <c r="B22" s="29">
+        <v>88520164</v>
+      </c>
+      <c r="C22" s="30">
+        <v>48.4</v>
+      </c>
+      <c r="D22" s="30">
+        <v>31.6</v>
+      </c>
+      <c r="E22" s="27">
         <v>65207</v>
       </c>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="12">
+      <c r="H22" s="11">
         <v>1913</v>
       </c>
-      <c r="I22" s="13">
+      <c r="I22" s="12">
         <f t="shared" si="0"/>
-        <v>4265630.4473999999</v>
-      </c>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="12">
+        <v>4284375.9375999998</v>
+      </c>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
+      <c r="L22" s="11">
         <v>1913</v>
       </c>
-      <c r="M22" s="13">
+      <c r="M22" s="12">
         <f t="shared" si="1"/>
-        <v>2787704.5455</v>
+        <v>2797237.1824000003</v>
       </c>
       <c r="N22" s="8"/>
       <c r="O22" s="8"/>
@@ -3766,16 +3766,16 @@
       <c r="A23" s="10">
         <v>1914</v>
       </c>
-      <c r="B23" s="11">
-        <v>90039648</v>
-      </c>
-      <c r="C23" s="10">
-        <v>47.9</v>
-      </c>
-      <c r="D23" s="10">
-        <v>31.1</v>
-      </c>
-      <c r="E23" s="30">
+      <c r="B23" s="29">
+        <v>90062796</v>
+      </c>
+      <c r="C23" s="30">
+        <v>48</v>
+      </c>
+      <c r="D23" s="30">
+        <v>31.2</v>
+      </c>
+      <c r="E23" s="27">
         <v>33340</v>
       </c>
       <c r="F23" s="8"/>
@@ -3796,10 +3796,10 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="8"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
@@ -3824,23 +3824,23 @@
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
       <c r="G25" s="8"/>
-      <c r="H25" s="26" t="s">
+      <c r="H25" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="I25" s="26"/>
-      <c r="J25" s="26"/>
-      <c r="K25" s="13">
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="12">
         <f>SUM(K14:K15)</f>
-        <v>218367.34025000036</v>
+        <v>222163.70539999893</v>
       </c>
       <c r="L25" s="8"/>
       <c r="M25" s="8"/>
       <c r="N25" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O25" s="13">
+      <c r="O25" s="12">
         <f>SUM(O13:O15)</f>
-        <v>116197.21039999882</v>
+        <v>114323.92399999918</v>
       </c>
       <c r="P25" s="8"/>
       <c r="Q25" s="8"/>
@@ -3856,21 +3856,21 @@
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="8"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="27"/>
-      <c r="J26" s="27"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="24"/>
       <c r="K26" s="8"/>
       <c r="L26" s="8"/>
       <c r="M26" s="8"/>
       <c r="N26" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="O26" s="13">
+      <c r="O26" s="12">
         <f>Q26*0.526246</f>
         <v>26813.286192</v>
       </c>
       <c r="P26" s="8"/>
-      <c r="Q26" s="13">
+      <c r="Q26" s="12">
         <v>50952</v>
       </c>
       <c r="R26" s="8"/>
@@ -3885,9 +3885,9 @@
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
       <c r="G27" s="8"/>
-      <c r="H27" s="27"/>
-      <c r="I27" s="27"/>
-      <c r="J27" s="27"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="24"/>
+      <c r="J27" s="24"/>
       <c r="K27" s="8"/>
       <c r="L27" s="8"/>
       <c r="M27" s="8"/>
@@ -3907,23 +3907,23 @@
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
       <c r="G28" s="8"/>
-      <c r="H28" s="26" t="s">
+      <c r="H28" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="I28" s="26"/>
-      <c r="J28" s="26"/>
-      <c r="K28" s="13">
+      <c r="I28" s="28"/>
+      <c r="J28" s="28"/>
+      <c r="K28" s="12">
         <f>K25*0.68</f>
-        <v>148489.79137000025</v>
-      </c>
-      <c r="L28" s="13"/>
-      <c r="M28" s="13"/>
+        <v>151071.31967199928</v>
+      </c>
+      <c r="L28" s="12"/>
+      <c r="M28" s="12"/>
       <c r="N28" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="O28" s="13">
+      <c r="O28" s="12">
         <f>O25-O26</f>
-        <v>89383.924207998818</v>
+        <v>87510.637807999185</v>
       </c>
       <c r="P28" s="8"/>
       <c r="Q28" s="8"/>
@@ -3939,14 +3939,14 @@
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
       <c r="G29" s="8"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
-      <c r="J29" s="27"/>
-      <c r="K29" s="13"/>
-      <c r="L29" s="13"/>
-      <c r="M29" s="13"/>
-      <c r="N29" s="13"/>
-      <c r="O29" s="13"/>
+      <c r="H29" s="24"/>
+      <c r="I29" s="24"/>
+      <c r="J29" s="24"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="12"/>
+      <c r="M29" s="12"/>
+      <c r="N29" s="12"/>
+      <c r="O29" s="12"/>
       <c r="P29" s="8"/>
       <c r="Q29" s="8"/>
       <c r="R29" s="8"/>
@@ -3961,14 +3961,14 @@
       <c r="E30" s="8"/>
       <c r="F30" s="8"/>
       <c r="G30" s="8"/>
-      <c r="H30" s="27"/>
-      <c r="I30" s="27"/>
-      <c r="J30" s="27"/>
-      <c r="K30" s="13"/>
-      <c r="L30" s="13"/>
-      <c r="M30" s="13"/>
-      <c r="N30" s="13"/>
-      <c r="O30" s="13"/>
+      <c r="H30" s="24"/>
+      <c r="I30" s="24"/>
+      <c r="J30" s="24"/>
+      <c r="K30" s="12"/>
+      <c r="L30" s="12"/>
+      <c r="M30" s="12"/>
+      <c r="N30" s="12"/>
+      <c r="O30" s="12"/>
       <c r="P30" s="8"/>
       <c r="Q30" s="8"/>
       <c r="R30" s="8"/>
@@ -3983,19 +3983,19 @@
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
       <c r="G31" s="8"/>
-      <c r="H31" s="26" t="s">
+      <c r="H31" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="I31" s="26"/>
-      <c r="J31" s="26"/>
-      <c r="K31" s="13">
+      <c r="I31" s="28"/>
+      <c r="J31" s="28"/>
+      <c r="K31" s="12">
         <f>K28+O28</f>
-        <v>237873.71557799907</v>
-      </c>
-      <c r="L31" s="13"/>
-      <c r="M31" s="13"/>
-      <c r="N31" s="13"/>
-      <c r="O31" s="13"/>
+        <v>238581.95747999847</v>
+      </c>
+      <c r="L31" s="12"/>
+      <c r="M31" s="12"/>
+      <c r="N31" s="12"/>
+      <c r="O31" s="12"/>
       <c r="P31" s="8"/>
       <c r="Q31" s="8"/>
       <c r="R31" s="8"/>
@@ -4010,14 +4010,14 @@
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
       <c r="G32" s="8"/>
-      <c r="H32" s="27"/>
-      <c r="I32" s="27"/>
-      <c r="J32" s="27"/>
-      <c r="K32" s="13"/>
-      <c r="L32" s="13"/>
-      <c r="M32" s="13"/>
-      <c r="N32" s="13"/>
-      <c r="O32" s="13"/>
+      <c r="H32" s="24"/>
+      <c r="I32" s="24"/>
+      <c r="J32" s="24"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="12"/>
+      <c r="N32" s="12"/>
+      <c r="O32" s="12"/>
       <c r="P32" s="8"/>
       <c r="Q32" s="8"/>
       <c r="R32" s="8"/>
@@ -4032,14 +4032,14 @@
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
       <c r="G33" s="8"/>
-      <c r="H33" s="27"/>
-      <c r="I33" s="27"/>
-      <c r="J33" s="27"/>
-      <c r="K33" s="13"/>
-      <c r="L33" s="13"/>
-      <c r="M33" s="13"/>
-      <c r="N33" s="13"/>
-      <c r="O33" s="13"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="24"/>
+      <c r="J33" s="24"/>
+      <c r="K33" s="12"/>
+      <c r="L33" s="12"/>
+      <c r="M33" s="12"/>
+      <c r="N33" s="12"/>
+      <c r="O33" s="12"/>
       <c r="P33" s="8"/>
       <c r="Q33" s="8"/>
       <c r="R33" s="8"/>
@@ -4054,14 +4054,14 @@
       <c r="E34" s="8"/>
       <c r="F34" s="8"/>
       <c r="G34" s="8"/>
-      <c r="H34" s="27"/>
-      <c r="I34" s="27"/>
-      <c r="J34" s="27"/>
-      <c r="K34" s="13"/>
-      <c r="L34" s="13"/>
-      <c r="M34" s="13"/>
-      <c r="N34" s="13"/>
-      <c r="O34" s="13"/>
+      <c r="H34" s="24"/>
+      <c r="I34" s="24"/>
+      <c r="J34" s="24"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="12"/>
+      <c r="M34" s="12"/>
+      <c r="N34" s="12"/>
+      <c r="O34" s="12"/>
       <c r="P34" s="8"/>
       <c r="Q34" s="8"/>
       <c r="R34" s="8"/>
@@ -4076,21 +4076,21 @@
       <c r="E35" s="8"/>
       <c r="F35" s="8"/>
       <c r="G35" s="8"/>
-      <c r="H35" s="26" t="s">
+      <c r="H35" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="I35" s="26"/>
-      <c r="J35" s="26"/>
-      <c r="K35" s="18">
+      <c r="I35" s="28"/>
+      <c r="J35" s="28"/>
+      <c r="K35" s="17">
         <f>K31/O26</f>
-        <v>8.8714868395717552</v>
-      </c>
-      <c r="L35" s="18"/>
-      <c r="M35" s="18"/>
-      <c r="N35" s="18"/>
-      <c r="O35" s="18">
+        <v>8.8979006814607331</v>
+      </c>
+      <c r="L35" s="17"/>
+      <c r="M35" s="17"/>
+      <c r="N35" s="17"/>
+      <c r="O35" s="17">
         <f>O28/O26</f>
-        <v>3.3335684245472068</v>
+        <v>3.2637043136513726</v>
       </c>
       <c r="P35" s="8"/>
       <c r="Q35" s="8"/>
@@ -4109,11 +4109,11 @@
       <c r="H36" s="8"/>
       <c r="I36" s="8"/>
       <c r="J36" s="8"/>
-      <c r="K36" s="13"/>
-      <c r="L36" s="13"/>
-      <c r="M36" s="13"/>
-      <c r="N36" s="13"/>
-      <c r="O36" s="13"/>
+      <c r="K36" s="12"/>
+      <c r="L36" s="12"/>
+      <c r="M36" s="12"/>
+      <c r="N36" s="12"/>
+      <c r="O36" s="12"/>
       <c r="P36" s="8"/>
       <c r="Q36" s="8"/>
       <c r="R36" s="8"/>
@@ -4131,11 +4131,11 @@
       <c r="H37" s="8"/>
       <c r="I37" s="8"/>
       <c r="J37" s="8"/>
-      <c r="K37" s="13"/>
-      <c r="L37" s="13"/>
-      <c r="M37" s="13"/>
-      <c r="N37" s="13"/>
-      <c r="O37" s="13"/>
+      <c r="K37" s="12"/>
+      <c r="L37" s="12"/>
+      <c r="M37" s="12"/>
+      <c r="N37" s="12"/>
+      <c r="O37" s="12"/>
       <c r="P37" s="8"/>
       <c r="Q37" s="8"/>
       <c r="R37" s="8"/>
@@ -4238,5 +4238,6 @@
     <mergeCell ref="H35:J35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>